--- a/AAII_Financials/Yearly/VWAGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VWAGY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>336117600</v>
+      </c>
+      <c r="E8" s="3">
         <v>356233000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>298225900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>284544500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>272641000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>283505800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>270035500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>275636400</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>227360500</v>
+        <v>209232800</v>
       </c>
       <c r="E9" s="3">
+        <v>227401300</v>
+      </c>
+      <c r="F9" s="3">
         <v>198146800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>189741800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>182663000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>190714800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>183345500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>188939700</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>64842500</v>
+        <v>58285500</v>
       </c>
       <c r="E10" s="3">
+        <v>64356100</v>
+      </c>
+      <c r="F10" s="3">
         <v>52917600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50630000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45009200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51881900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50820900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>50074400</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>18597200</v>
+      </c>
+      <c r="E12" s="3">
         <v>17490900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15313700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14545700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14747400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14812000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13872200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13945700</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +862,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1534200</v>
+        <v>4522200</v>
       </c>
       <c r="E14" s="3">
+        <v>1092100</v>
+      </c>
+      <c r="F14" s="3">
         <v>4098500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>437800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2759600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2569900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5461400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3149600</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>11441100</v>
+      </c>
+      <c r="E15" s="3">
         <v>11234700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12527500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13174100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14058700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12694400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12095300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12331900</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>329017400</v>
+        <v>312390500</v>
       </c>
       <c r="E17" s="3">
+        <v>329595400</v>
+      </c>
+      <c r="F17" s="3">
         <v>273572700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>262575900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>258203100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>262037900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>249638200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>257521600</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>27215700</v>
+        <v>23727100</v>
       </c>
       <c r="E18" s="3">
+        <v>26637600</v>
+      </c>
+      <c r="F18" s="3">
         <v>24653200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21968600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14437900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21467800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20397300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18114800</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-987100</v>
+        <v>743300</v>
       </c>
       <c r="E20" s="3">
+        <v>-1072200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2050900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2504300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4425700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3512500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2925300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2370300</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>39437400</v>
+        <v>34424900</v>
       </c>
       <c r="E21" s="3">
+        <v>38944400</v>
+      </c>
+      <c r="F21" s="3">
         <v>39231600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37647000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>32922300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>37674800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35417900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32817000</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>3970400</v>
+        <v>3567700</v>
       </c>
       <c r="E22" s="3">
+        <v>4023400</v>
+      </c>
+      <c r="F22" s="3">
         <v>436000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2067600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2802400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2832500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1057900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2059300</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>25636100</v>
+        <v>17398300</v>
       </c>
       <c r="E23" s="3">
+        <v>25532200</v>
+      </c>
+      <c r="F23" s="3">
         <v>23585600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22888700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14271600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20599300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17910500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16418100</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>5819600</v>
+        <v>4566700</v>
       </c>
       <c r="E24" s="3">
+        <v>5788700</v>
+      </c>
+      <c r="F24" s="3">
         <v>6644200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5342900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3477700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4855800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3995900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2653700</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>19816500</v>
+        <v>12831600</v>
       </c>
       <c r="E26" s="3">
+        <v>19743600</v>
+      </c>
+      <c r="F26" s="3">
         <v>16941300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17545800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10793900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15743500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13914600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13764400</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>17699800</v>
+        <v>11099500</v>
       </c>
       <c r="E27" s="3">
+        <v>17626800</v>
+      </c>
+      <c r="F27" s="3">
         <v>15903600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16880500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10194500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14977000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13541300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13423400</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1277,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1307,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>987100</v>
+        <v>-743300</v>
       </c>
       <c r="E32" s="3">
+        <v>1072200</v>
+      </c>
+      <c r="F32" s="3">
         <v>2050900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2504300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4425700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3512500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2925300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2370300</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>18347500</v>
+        <v>11751700</v>
       </c>
       <c r="E33" s="3">
+        <v>18274600</v>
+      </c>
+      <c r="F33" s="3">
         <v>16519200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17493500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10846500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15583000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13895100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13752400</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>18347500</v>
+        <v>11751700</v>
       </c>
       <c r="E35" s="3">
+        <v>18274600</v>
+      </c>
+      <c r="F35" s="3">
         <v>16519200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17493500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10846500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15583000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13895100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13752400</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,251 +1553,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>24950800</v>
+      </c>
+      <c r="E41" s="3">
         <v>31721000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24617900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28990100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29629400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22085100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27672300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16600600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>23914500</v>
+      </c>
+      <c r="E42" s="3">
         <v>24550700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35126600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>20100100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21411600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15201400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19925600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20770900</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>44295500</v>
+      </c>
+      <c r="E43" s="3">
         <v>45616200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>37321800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>35011900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38203100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37080000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36046500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30510300</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>52361500</v>
+      </c>
+      <c r="E44" s="3">
         <v>53821200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>52119300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>45902400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>47773700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>47018300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>47288800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>43363400</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>9575500</v>
+      </c>
+      <c r="E45" s="3">
         <v>8919000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8975100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8055300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8333900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7150700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2344900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3526700</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>253888600</v>
+      </c>
+      <c r="E46" s="3">
         <v>264887800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>239562900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>227848300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>238463600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>210372600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>210139700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>192257400</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>16564900</v>
+      </c>
+      <c r="E47" s="3">
         <v>18426000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17267300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17662900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14611600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11301800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12659700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13634700</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>73103800</v>
+      </c>
+      <c r="E48" s="3">
         <v>73278400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>68597800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73922400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78677700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>75329400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68602000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66815600</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>96080300</v>
+      </c>
+      <c r="E49" s="3">
         <v>97826900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>88540100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>87899500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82912500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74077000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73739400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>75901800</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1880,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>9549600</v>
+      </c>
+      <c r="E52" s="3">
         <v>10308400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12887700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9965900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9870300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6593000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>96409400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8668300</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>663576900</v>
+        <v>655249000</v>
       </c>
       <c r="E54" s="3">
+        <v>663920600</v>
+      </c>
+      <c r="F54" s="3">
         <v>602771200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>601170200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>608090500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>547717400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>524566100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>506956100</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>27145700</v>
+      </c>
+      <c r="E57" s="3">
         <v>29664000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27901000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23856500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23902100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21998700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24000500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24613400</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>121151300</v>
+      </c>
+      <c r="E58" s="3">
         <v>122113400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>89182400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>89371100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>108437900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98655600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>102767300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>98275700</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>51836000</v>
+        <v>54906300</v>
       </c>
       <c r="E59" s="3">
+        <v>51808300</v>
+      </c>
+      <c r="F59" s="3">
         <v>56843000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53334500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49765100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48214600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48276800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52422000</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>227560500</v>
+        <v>224701300</v>
       </c>
       <c r="E60" s="3">
+        <v>227739600</v>
+      </c>
+      <c r="F60" s="3">
         <v>195279500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>186958900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>202336400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>188445700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>192315100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>192590100</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>26062700</v>
+      </c>
+      <c r="E61" s="3">
         <v>19946900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23373900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28022300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19126600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19740800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16243400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8056000</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>39543500</v>
+        <v>37155000</v>
       </c>
       <c r="E62" s="3">
+        <v>40510700</v>
+      </c>
+      <c r="F62" s="3">
         <v>39152500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38634100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39877700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35172300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33539000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35954600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>453659800</v>
+        <v>451572600</v>
       </c>
       <c r="E66" s="3">
+        <v>454806000</v>
+      </c>
+      <c r="F66" s="3">
         <v>412188700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>434953900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>450557800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>408955200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>390215300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>375978600</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>163402200</v>
+        <v>160606700</v>
       </c>
       <c r="E72" s="3">
+        <v>162599800</v>
+      </c>
+      <c r="F72" s="3">
         <v>146705100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>133449300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>123268500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>108774500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>104310700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>97560000</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>194201400</v>
+        <v>188729700</v>
       </c>
       <c r="E76" s="3">
+        <v>193398900</v>
+      </c>
+      <c r="F76" s="3">
         <v>176740400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164277300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>155411600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>136663700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>134093200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>130702400</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>18347500</v>
+        <v>11751700</v>
       </c>
       <c r="E81" s="3">
+        <v>18274600</v>
+      </c>
+      <c r="F81" s="3">
         <v>16519200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17493500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10846500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15583000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13895100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13752400</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>11301400</v>
+      </c>
+      <c r="E83" s="3">
         <v>11182700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12604500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13476600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14457500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12985100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11325900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11330500</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>17756500</v>
+      </c>
+      <c r="E89" s="3">
         <v>21394900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30454200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>43936100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30459900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20180700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8326100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1422900</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-17809300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16196500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13837800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12117600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13789600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15969000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15719000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15672400</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-32687600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21899000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44695900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29714500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27755400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23730200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24719500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19822300</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>5357700</v>
+      </c>
+      <c r="E96" s="3">
         <v>12967800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4661800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3405000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3536400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3243200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2714700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1593400</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>11533300</v>
+      </c>
+      <c r="E100" s="3">
         <v>17694300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4515300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8818400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9341900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-970700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28126900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21163500</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1949800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-304600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1071300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-911300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>272700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-198100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-873000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-3340900</v>
+      </c>
+      <c r="E102" s="3">
         <v>15240400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10031000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6474500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11135200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4247600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11535400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-954600</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VWAGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VWAGY_YR_FIN.xlsx
@@ -738,13 +738,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>209232800</v>
+        <v>220088000</v>
       </c>
       <c r="E9" s="3">
-        <v>227401300</v>
+        <v>236208700</v>
       </c>
       <c r="F9" s="3">
-        <v>198146800</v>
+        <v>201698200</v>
       </c>
       <c r="G9" s="3">
         <v>189741800</v>
